--- a/erp-server/erp-server-file/src/main/resources/excel/tms/tmsCfgSailingExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/tmsCfgSailingExport.xlsx
@@ -32,6 +32,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -246,7 +253,7 @@
     <t>{.startTime}</t>
   </si>
   <si>
-    <t>{.effectiveDate}</t>
+    <t>{.effectiveDateStr}</t>
   </si>
   <si>
     <t>·</t>
@@ -256,11 +263,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="[$-409]yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -901,17 +909,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1233,67 +1247,67 @@
     <col min="3" max="3" width="18.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="17.375" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="6" max="6" width="16.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" spans="1:9">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>17</v>
       </c>
     </row>
